--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TIBU-RON CASTELLDEFELS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_TIBU-RON CASTELLDEFELS.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>45.5562</v>
+        <v>38.91079999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>43.2301</v>
+        <v>46.1543</v>
       </c>
       <c r="F2" t="n">
-        <v>2.326300000000001</v>
+        <v>-7.243399999999999</v>
       </c>
       <c r="G2" t="n">
         <v>-10.5254</v>
@@ -610,13 +610,13 @@
         <v>56.3409</v>
       </c>
       <c r="S2" t="n">
-        <v>18.3084</v>
+        <v>11.6629</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5331</v>
+        <v>1.3917</v>
       </c>
       <c r="U2" t="n">
-        <v>19.8414</v>
+        <v>10.2712</v>
       </c>
       <c r="V2" t="n">
         <v>39.9555</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>33.3992</v>
+        <v>31.6824</v>
       </c>
       <c r="E3" t="n">
-        <v>33.0107</v>
+        <v>25.8771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3887999999999994</v>
+        <v>5.8051</v>
       </c>
       <c r="G3" t="n">
-        <v>6.575600000000001</v>
+        <v>2.4497</v>
       </c>
       <c r="H3" t="n">
-        <v>10.4883</v>
+        <v>9.099600000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.9124</v>
+        <v>-6.6498</v>
       </c>
       <c r="J3" t="n">
-        <v>35.3304</v>
+        <v>26.4891</v>
       </c>
       <c r="K3" t="n">
-        <v>26.0104</v>
+        <v>24.5249</v>
       </c>
       <c r="L3" t="n">
-        <v>9.3201</v>
+        <v>1.9642</v>
       </c>
       <c r="M3" t="n">
-        <v>-28.7543</v>
+        <v>-24.0393</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.522</v>
+        <v>-15.4252</v>
       </c>
       <c r="O3" t="n">
-        <v>-13.2325</v>
+        <v>-8.614000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5708</v>
+        <v>22.6159</v>
       </c>
       <c r="Q3" t="n">
-        <v>-29.3606</v>
+        <v>-12.4981</v>
       </c>
       <c r="R3" t="n">
-        <v>32.9318</v>
+        <v>35.1139</v>
       </c>
       <c r="S3" t="n">
-        <v>10.4791</v>
+        <v>-1.6477</v>
       </c>
       <c r="T3" t="n">
-        <v>8.612</v>
+        <v>-2.8381</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8668</v>
+        <v>1.1904</v>
       </c>
       <c r="V3" t="n">
-        <v>12.7741</v>
+        <v>8.265000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>18.4291</v>
+        <v>14.7247</v>
       </c>
       <c r="X3" t="n">
-        <v>-5.654999999999999</v>
+        <v>-6.4596</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>32.943</v>
+        <v>29.6812</v>
       </c>
       <c r="E4" t="n">
-        <v>33.6487</v>
+        <v>27.824</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7058</v>
+        <v>1.857500000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>28.8023</v>
+        <v>6.575600000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>23.3803</v>
+        <v>10.4883</v>
       </c>
       <c r="I4" t="n">
-        <v>5.421600000000001</v>
+        <v>-3.9124</v>
       </c>
       <c r="J4" t="n">
-        <v>28.8023</v>
+        <v>35.3304</v>
       </c>
       <c r="K4" t="n">
-        <v>23.3803</v>
+        <v>26.0104</v>
       </c>
       <c r="L4" t="n">
-        <v>5.421600000000001</v>
+        <v>9.3201</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-28.7543</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-15.522</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-13.2325</v>
       </c>
       <c r="P4" t="n">
-        <v>-37.6927</v>
+        <v>3.5708</v>
       </c>
       <c r="Q4" t="n">
-        <v>-37.6927</v>
+        <v>-29.3606</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>32.9318</v>
       </c>
       <c r="S4" t="n">
-        <v>56.9332</v>
+        <v>6.7607</v>
       </c>
       <c r="T4" t="n">
-        <v>40.1318</v>
+        <v>3.4252</v>
       </c>
       <c r="U4" t="n">
-        <v>16.8014</v>
+        <v>3.3355</v>
       </c>
       <c r="V4" t="n">
-        <v>-15.0998</v>
+        <v>12.7741</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4078</v>
+        <v>18.4291</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.5077</v>
+        <v>-5.654999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>22.1295</v>
+        <v>24.0107</v>
       </c>
       <c r="E5" t="n">
-        <v>27.4561</v>
+        <v>28.2101</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.327100000000001</v>
+        <v>-4.1995</v>
       </c>
       <c r="G5" t="n">
         <v>25.2043</v>
@@ -844,13 +844,13 @@
         <v>44.835</v>
       </c>
       <c r="S5" t="n">
-        <v>6.470800000000001</v>
+        <v>8.3521</v>
       </c>
       <c r="T5" t="n">
-        <v>3.0177</v>
+        <v>3.7713</v>
       </c>
       <c r="U5" t="n">
-        <v>3.453</v>
+        <v>4.580500000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.6102</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,78 +874,74 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>21.0345</v>
+        <v>22.9355</v>
       </c>
       <c r="E6" t="n">
-        <v>18.6787</v>
+        <v>11.9363</v>
       </c>
       <c r="F6" t="n">
-        <v>2.356</v>
+        <v>10.999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4497</v>
+        <v>8.161900000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>9.099600000000001</v>
+        <v>11.8422</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.6498</v>
+        <v>-3.6807</v>
       </c>
       <c r="J6" t="n">
-        <v>26.4891</v>
+        <v>21.0953</v>
       </c>
       <c r="K6" t="n">
-        <v>24.5249</v>
+        <v>22.8661</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9642</v>
+        <v>-1.770700000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-24.0393</v>
+        <v>-12.9336</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.4252</v>
+        <v>-11.0237</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.614000000000001</v>
+        <v>-1.909799999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>22.6159</v>
+        <v>11.1094</v>
       </c>
       <c r="Q6" t="n">
-        <v>-12.4981</v>
+        <v>-21.4253</v>
       </c>
       <c r="R6" t="n">
-        <v>35.1139</v>
+        <v>32.5349</v>
       </c>
       <c r="S6" t="n">
-        <v>-12.2957</v>
+        <v>3.8189</v>
       </c>
       <c r="T6" t="n">
-        <v>-10.0367</v>
+        <v>0.6816</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.2589</v>
+        <v>3.1372</v>
       </c>
       <c r="V6" t="n">
-        <v>8.265000000000001</v>
+        <v>-0.1546999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>14.7247</v>
+        <v>11.5851</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.4596</v>
+        <v>-11.7398</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>J. ARNAL DIAZ</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -955,73 +951,73 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>16.1062</v>
+        <v>11.6946</v>
       </c>
       <c r="E7" t="n">
-        <v>6.840600000000001</v>
+        <v>6.1003</v>
       </c>
       <c r="F7" t="n">
-        <v>9.265600000000001</v>
+        <v>5.5945</v>
       </c>
       <c r="G7" t="n">
-        <v>8.161900000000001</v>
+        <v>-23.785</v>
       </c>
       <c r="H7" t="n">
-        <v>11.8422</v>
+        <v>-16.5392</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.6807</v>
+        <v>-7.2454</v>
       </c>
       <c r="J7" t="n">
-        <v>21.0953</v>
+        <v>8.8588</v>
       </c>
       <c r="K7" t="n">
-        <v>22.8661</v>
+        <v>5.8064</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.770700000000001</v>
+        <v>3.0524</v>
       </c>
       <c r="M7" t="n">
-        <v>-12.9336</v>
+        <v>-32.6436</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.0237</v>
+        <v>-22.3455</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.909799999999999</v>
+        <v>-10.2982</v>
       </c>
       <c r="P7" t="n">
-        <v>11.1094</v>
+        <v>38.4864</v>
       </c>
       <c r="Q7" t="n">
-        <v>-21.4253</v>
+        <v>-1.3888</v>
       </c>
       <c r="R7" t="n">
-        <v>32.5349</v>
+        <v>39.8751</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.0102</v>
+        <v>-2.8861</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.414099999999999</v>
+        <v>-1.37</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4033</v>
+        <v>-1.5162</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1546999999999999</v>
+        <v>-0.1206</v>
       </c>
       <c r="W7" t="n">
-        <v>11.5851</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-11.7398</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1026,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>11.2252</v>
+        <v>11.6946</v>
       </c>
       <c r="E8" t="n">
-        <v>14.5943</v>
+        <v>6.1003</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3688</v>
+        <v>5.5945</v>
       </c>
       <c r="G8" t="n">
-        <v>11.9461</v>
+        <v>-23.785</v>
       </c>
       <c r="H8" t="n">
-        <v>11.8508</v>
+        <v>-16.5392</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09499999999999997</v>
+        <v>-7.2454</v>
       </c>
       <c r="J8" t="n">
-        <v>24.2812</v>
+        <v>8.8588</v>
       </c>
       <c r="K8" t="n">
-        <v>17.1648</v>
+        <v>5.8064</v>
       </c>
       <c r="L8" t="n">
-        <v>7.116099999999999</v>
+        <v>3.0524</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.3348</v>
+        <v>-32.6436</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.3138</v>
+        <v>-22.3455</v>
       </c>
       <c r="O8" t="n">
-        <v>-7.0209</v>
+        <v>-10.2982</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.3644</v>
+        <v>38.4864</v>
       </c>
       <c r="Q8" t="n">
-        <v>-26.7816</v>
+        <v>-1.3888</v>
       </c>
       <c r="R8" t="n">
-        <v>22.4176</v>
+        <v>39.8751</v>
       </c>
       <c r="S8" t="n">
-        <v>17.342</v>
+        <v>-2.8861</v>
       </c>
       <c r="T8" t="n">
-        <v>14.7725</v>
+        <v>-1.37</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5695</v>
+        <v>-1.5162</v>
       </c>
       <c r="V8" t="n">
-        <v>-13.6985</v>
+        <v>-0.1206</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3226</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-16.0209</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. GARCÍA CARACUEL</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1104,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1838</v>
+        <v>9.5122</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5161</v>
+        <v>10.9505</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6677</v>
+        <v>-1.4384</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6822</v>
+        <v>-27.2615</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9151</v>
+        <v>-17.2146</v>
       </c>
       <c r="I9" t="n">
-        <v>0.767</v>
+        <v>-10.0472</v>
       </c>
       <c r="J9" t="n">
-        <v>2.661</v>
+        <v>6.6381</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5807</v>
+        <v>8.965900000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0803</v>
+        <v>-2.328</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0212</v>
+        <v>-33.8997</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6655</v>
+        <v>-26.1806</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6867</v>
+        <v>-7.7196</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1903</v>
+        <v>7.1418</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1984</v>
+        <v>-38.6848</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3887</v>
+        <v>45.8266</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5016</v>
+        <v>3.8284</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2438</v>
+        <v>-1.4089</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2579</v>
+        <v>5.2374</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8097</v>
+        <v>25.8032</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8097</v>
+        <v>44.4062</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-18.603</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>H. GARCÍA CARACUEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1182,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>6.072099999999997</v>
+        <v>6.12</v>
       </c>
       <c r="E10" t="n">
-        <v>6.971699999999998</v>
+        <v>4.312</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8996000000000013</v>
+        <v>1.808</v>
       </c>
       <c r="G10" t="n">
-        <v>-27.2615</v>
+        <v>2.6822</v>
       </c>
       <c r="H10" t="n">
-        <v>-17.2146</v>
+        <v>1.9151</v>
       </c>
       <c r="I10" t="n">
-        <v>-10.0472</v>
+        <v>0.767</v>
       </c>
       <c r="J10" t="n">
-        <v>6.6381</v>
+        <v>2.661</v>
       </c>
       <c r="K10" t="n">
-        <v>8.965900000000001</v>
+        <v>2.5807</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.328</v>
+        <v>0.0803</v>
       </c>
       <c r="M10" t="n">
-        <v>-33.8997</v>
+        <v>0.0212</v>
       </c>
       <c r="N10" t="n">
-        <v>-26.1806</v>
+        <v>-0.6655</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.7196</v>
+        <v>0.6867</v>
       </c>
       <c r="P10" t="n">
-        <v>7.1418</v>
+        <v>1.1903</v>
       </c>
       <c r="Q10" t="n">
-        <v>-38.6848</v>
+        <v>-0.1984</v>
       </c>
       <c r="R10" t="n">
-        <v>45.8266</v>
+        <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3887</v>
+        <v>0.4379</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.3879</v>
+        <v>0.0397</v>
       </c>
       <c r="U10" t="n">
-        <v>5.776400000000001</v>
+        <v>0.3981</v>
       </c>
       <c r="V10" t="n">
-        <v>25.8032</v>
+        <v>1.8097</v>
       </c>
       <c r="W10" t="n">
-        <v>44.4062</v>
+        <v>1.8097</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. MUÑOZ ALCÓN</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1260,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1594</v>
+        <v>2.194199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.218</v>
+        <v>5.0318</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3774</v>
+        <v>-2.837299999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3691</v>
+        <v>11.9461</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1259</v>
+        <v>11.8508</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4949</v>
+        <v>0.09499999999999997</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0856</v>
+        <v>24.2812</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0053</v>
+        <v>17.1648</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0803</v>
+        <v>7.116099999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2835</v>
+        <v>-12.3348</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1312</v>
+        <v>-5.3138</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4146</v>
+        <v>-7.0209</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1984</v>
+        <v>-4.3644</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>-26.7816</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7935</v>
+        <v>22.4176</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0113</v>
+        <v>8.311199999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3117</v>
+        <v>5.210100000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3004</v>
+        <v>3.1008</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-13.6985</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.3226</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-16.0209</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LARA</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1338,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5125</v>
+        <v>1.6635</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0341</v>
+        <v>9.569600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4785</v>
+        <v>-7.9063</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6525</v>
+        <v>28.8023</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3180999999999999</v>
+        <v>23.3803</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3344</v>
+        <v>5.421600000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1821</v>
+        <v>28.8023</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7392</v>
+        <v>23.3803</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5571</v>
+        <v>5.421600000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8346</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0573</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7771999999999999</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3967999999999999</v>
+        <v>-37.6927</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.5871</v>
+        <v>-37.6927</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9908</v>
+        <v>25.6537</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6291</v>
+        <v>16.0527</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3618</v>
+        <v>9.601599999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.266</v>
+        <v>-15.0998</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.4078</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.266</v>
+        <v>-17.5077</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. ELIAS ALONSO</t>
+          <t>P. MUÑOZ ALCÓN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1416,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4204</v>
+        <v>0.4258</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1843</v>
+        <v>-0.9516</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2360999999999999</v>
+        <v>1.3774</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3065</v>
+        <v>0.3691</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4595</v>
+        <v>-0.1259</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1531</v>
+        <v>0.4949</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3785999999999999</v>
+        <v>0.0856</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5794</v>
+        <v>0.0053</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2008</v>
+        <v>0.0803</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9278000000000001</v>
+        <v>0.2835</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8801</v>
+        <v>-0.1312</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9523</v>
+        <v>0.4146</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7936</v>
+        <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1933</v>
+        <v>0.2551</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6234</v>
+        <v>-0.0453</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4302</v>
+        <v>0.3004</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5318999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5318999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,150 +1494,154 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.9631</v>
+        <v>-0.3524000000000012</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6577</v>
+        <v>21.9712</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3052000000000006</v>
+        <v>-22.3232</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1656</v>
+        <v>1.883099999999997</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.6761</v>
+        <v>-10.4144</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8416</v>
+        <v>12.2977</v>
       </c>
       <c r="J14" t="n">
-        <v>6.8139</v>
+        <v>36.4603</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4108</v>
+        <v>10.561</v>
       </c>
       <c r="L14" t="n">
-        <v>4.403</v>
+        <v>25.899</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.6485</v>
+        <v>-34.5768</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.087</v>
+        <v>-20.9754</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4384</v>
+        <v>-13.6016</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7773</v>
+        <v>2.5792</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.7288</v>
+        <v>-35.7089</v>
       </c>
       <c r="R14" t="n">
-        <v>11.5063</v>
+        <v>38.288</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.6787</v>
+        <v>-2.2289</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.743</v>
+        <v>0.2685999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9361</v>
+        <v>-2.4972</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.2269</v>
+        <v>-2.5859</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>20.9514</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.2269</v>
+        <v>-23.5375</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G. LOZANO MASSANET</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.1216</v>
+        <v>-1.0558</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.0794</v>
+        <v>-2.509399999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.042199999999999</v>
+        <v>1.4539</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.785</v>
+        <v>2.1656</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.5392</v>
+        <v>-3.6761</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.2454</v>
+        <v>5.8416</v>
       </c>
       <c r="J15" t="n">
-        <v>8.8588</v>
+        <v>6.8139</v>
       </c>
       <c r="K15" t="n">
-        <v>5.8064</v>
+        <v>2.4108</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0524</v>
+        <v>4.403</v>
       </c>
       <c r="M15" t="n">
-        <v>-32.6436</v>
+        <v>-4.6485</v>
       </c>
       <c r="N15" t="n">
-        <v>-22.3455</v>
+        <v>-6.087</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.2982</v>
+        <v>1.4384</v>
       </c>
       <c r="P15" t="n">
-        <v>38.4864</v>
+        <v>2.7773</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3888</v>
+        <v>-8.7288</v>
       </c>
       <c r="R15" t="n">
-        <v>39.8751</v>
+        <v>11.5063</v>
       </c>
       <c r="S15" t="n">
-        <v>-27.7024</v>
+        <v>0.2283000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-16.5494</v>
+        <v>-0.5946</v>
       </c>
       <c r="U15" t="n">
-        <v>-11.153</v>
+        <v>0.8228</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1206</v>
+        <v>-6.2269</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1206</v>
+        <v>-6.2269</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>A. RODRIGUEZ LARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1650,76 +1650,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-13.1216</v>
+        <v>-2.2983</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.0794</v>
+        <v>-0.9319999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.042199999999999</v>
+        <v>-1.3662</v>
       </c>
       <c r="G16" t="n">
-        <v>-23.785</v>
+        <v>-1.6525</v>
       </c>
       <c r="H16" t="n">
-        <v>-16.5392</v>
+        <v>-0.3180999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-7.2454</v>
+        <v>-1.3344</v>
       </c>
       <c r="J16" t="n">
-        <v>8.8588</v>
+        <v>1.1821</v>
       </c>
       <c r="K16" t="n">
-        <v>5.8064</v>
+        <v>1.7392</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0524</v>
+        <v>-0.5571</v>
       </c>
       <c r="M16" t="n">
-        <v>-32.6436</v>
+        <v>-2.8346</v>
       </c>
       <c r="N16" t="n">
-        <v>-22.3455</v>
+        <v>-2.0573</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.2982</v>
+        <v>-0.7771999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>38.4864</v>
+        <v>0.3967999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3888</v>
+        <v>-1.5871</v>
       </c>
       <c r="R16" t="n">
-        <v>39.8751</v>
+        <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-27.7024</v>
+        <v>-0.7765</v>
       </c>
       <c r="T16" t="n">
-        <v>-16.5494</v>
+        <v>-0.5271</v>
       </c>
       <c r="U16" t="n">
-        <v>-11.153</v>
+        <v>-0.2496</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1206</v>
+        <v>-0.266</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1206</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>N. ELIAS ALONSO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1728,76 +1728,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.2027</v>
+        <v>-3.1718</v>
       </c>
       <c r="E17" t="n">
-        <v>14.9139</v>
+        <v>-3.0199</v>
       </c>
       <c r="F17" t="n">
-        <v>-30.1169</v>
+        <v>-0.1519000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.883099999999997</v>
+        <v>-1.3065</v>
       </c>
       <c r="H17" t="n">
-        <v>-10.4144</v>
+        <v>-2.4595</v>
       </c>
       <c r="I17" t="n">
-        <v>12.2977</v>
+        <v>1.1531</v>
       </c>
       <c r="J17" t="n">
-        <v>36.4603</v>
+        <v>-0.3785999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>10.561</v>
+        <v>-0.5794</v>
       </c>
       <c r="L17" t="n">
-        <v>25.899</v>
+        <v>0.2008</v>
       </c>
       <c r="M17" t="n">
-        <v>-34.5768</v>
+        <v>-0.9278000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-20.9754</v>
+        <v>-1.8801</v>
       </c>
       <c r="O17" t="n">
-        <v>-13.6016</v>
+        <v>0.9523</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5792</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-35.7089</v>
+        <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
-        <v>38.288</v>
+        <v>0.7936</v>
       </c>
       <c r="S17" t="n">
-        <v>-17.0792</v>
+        <v>0.05530000000000002</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.788600000000001</v>
+        <v>-0.459</v>
       </c>
       <c r="U17" t="n">
-        <v>-10.2906</v>
+        <v>0.5144</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.5859</v>
+        <v>-0.5318999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>20.9514</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-23.5375</v>
+        <v>-0.5318999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ FLAQUE</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1806,76 +1806,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.7968</v>
+        <v>-8.360399999999998</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.7584</v>
+        <v>5.020300000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0383</v>
+        <v>-13.3804</v>
       </c>
       <c r="G18" t="n">
-        <v>-10.8899</v>
+        <v>-11.2129</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.6955</v>
+        <v>-3.0419</v>
       </c>
       <c r="I18" t="n">
-        <v>-7.194199999999999</v>
+        <v>-8.171199999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-8.421299999999999</v>
+        <v>24.4995</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.5934</v>
+        <v>20.086</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.827900000000001</v>
+        <v>4.4134</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4687</v>
+        <v>-35.7124</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1022</v>
+        <v>-23.1275</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3664</v>
+        <v>-12.5848</v>
       </c>
       <c r="P18" t="n">
-        <v>4.1662</v>
+        <v>7.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1741</v>
+        <v>-30.3528</v>
       </c>
       <c r="R18" t="n">
-        <v>7.3404</v>
+        <v>37.693</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.1234</v>
+        <v>-5.6398</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.3575</v>
+        <v>-1.4379</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.7659</v>
+        <v>-4.202</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.9493</v>
+        <v>1.1524</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1947</v>
+        <v>12.3117</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.1441</v>
+        <v>-11.1592</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>G. RODRIGUEZ FLAQUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1884,70 +1884,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>-20.5559</v>
+        <v>-12.5249</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.631800000000001</v>
+        <v>-10.9413</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.9238</v>
+        <v>-1.5837</v>
       </c>
       <c r="G19" t="n">
-        <v>-11.2129</v>
+        <v>-10.8899</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.0419</v>
+        <v>-3.6955</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.171199999999999</v>
+        <v>-7.194199999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>24.4995</v>
+        <v>-8.421299999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>20.086</v>
+        <v>-2.5934</v>
       </c>
       <c r="L19" t="n">
-        <v>4.4134</v>
+        <v>-5.827900000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-35.7124</v>
+        <v>-2.4687</v>
       </c>
       <c r="N19" t="n">
-        <v>-23.1275</v>
+        <v>-1.1022</v>
       </c>
       <c r="O19" t="n">
-        <v>-12.5848</v>
+        <v>-1.3664</v>
       </c>
       <c r="P19" t="n">
-        <v>7.34</v>
+        <v>4.1662</v>
       </c>
       <c r="Q19" t="n">
-        <v>-30.3528</v>
+        <v>-3.1741</v>
       </c>
       <c r="R19" t="n">
-        <v>37.693</v>
+        <v>7.3404</v>
       </c>
       <c r="S19" t="n">
-        <v>-17.8351</v>
+        <v>-0.8517</v>
       </c>
       <c r="T19" t="n">
-        <v>-9.0901</v>
+        <v>0.4594</v>
       </c>
       <c r="U19" t="n">
-        <v>-8.7454</v>
+        <v>-1.3113</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1524</v>
+        <v>-4.9493</v>
       </c>
       <c r="W19" t="n">
-        <v>12.3117</v>
+        <v>0.1947</v>
       </c>
       <c r="X19" t="n">
-        <v>-11.1592</v>
+        <v>-5.1441</v>
       </c>
     </row>
     <row r="20">
@@ -1965,19 +1965,19 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>105.1145</v>
+        <v>162.7619</v>
       </c>
       <c r="E20" t="n">
-        <v>159.2178</v>
+        <v>190.7036</v>
       </c>
       <c r="F20" t="n">
-        <v>-54.1027</v>
+        <v>-27.9404</v>
       </c>
       <c r="G20" t="n">
-        <v>-20.1788</v>
+        <v>-20.17880000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>14.66239999999999</v>
+        <v>14.66240000000001</v>
       </c>
       <c r="I20" t="n">
         <v>-34.8412</v>
@@ -2010,16 +2010,16 @@
         <v>449.5382</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.198700000000002</v>
+        <v>52.4477</v>
       </c>
       <c r="T20" t="n">
-        <v>-10.23619999999999</v>
+        <v>21.2494</v>
       </c>
       <c r="U20" t="n">
-        <v>5.035600000000004</v>
+        <v>31.1978</v>
       </c>
       <c r="V20" t="n">
-        <v>44.39550000000001</v>
+        <v>44.39549999999999</v>
       </c>
       <c r="W20" t="n">
         <v>204.252</v>
